--- a/BackEnd/Server/Controllers/FastReport/TaxTemplates/Phieu_xuat_kho_2_sheet.xlsx
+++ b/BackEnd/Server/Controllers/FastReport/TaxTemplates/Phieu_xuat_kho_2_sheet.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\BUSINESS DEVELOPMENT\PHAM MEM SAO BAC DAU\UP PM THUE\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5122190C-E886-4767-B386-1E4CFA0566DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="19320" windowHeight="14880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="19320" windowHeight="12220"/>
   </bookViews>
   <sheets>
     <sheet name="CT" sheetId="1" r:id="rId1"/>
@@ -38,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Mã hàng</t>
   </si>
@@ -67,12 +61,6 @@
     <t>HT_TT</t>
   </si>
   <si>
-    <t>B¸n hµng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONGTY  </t>
-  </si>
-  <si>
     <t>M· kh¸ch</t>
   </si>
   <si>
@@ -103,82 +91,19 @@
     <t>Ngµy</t>
   </si>
   <si>
-    <t>C23TND</t>
-  </si>
-  <si>
-    <t>TM/CK</t>
-  </si>
-  <si>
     <t>Tªn hµng hãa</t>
   </si>
   <si>
-    <t xml:space="preserve">K.H1014 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">K.H1015 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">K.H1016 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">K.H1017 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">M¸y biÕn ¸p 1 pha 50 kVA 22/0,23 kV                                                             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BA013DL2        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">M¸y biÕn ¸p 3 pha 100 kVA 22/0,4 kV                                                             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BA035DL2        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MBA 3P 630KVA 15-22/0.4KV                                                                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BA043DL2        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MBA 3P 100KVA 380/230KV                                                                         </t>
-  </si>
-  <si>
-    <t>BA004DL2</t>
-  </si>
-  <si>
     <t>Số phiếu/số hoá đơn</t>
   </si>
   <si>
-    <t>KHHH</t>
-  </si>
-  <si>
     <t>Sè phiÕu/sè hãa ®¬n</t>
-  </si>
-  <si>
-    <t>c«ng ty tnhh kinh doanh thiÕt bÞ ®iÖn b×nh an</t>
-  </si>
-  <si>
-    <t>274/39/41 NguyÔn V¨n T¹o, Êp 2, X· Long Thíi, HuyÖn Nhµ BÌ, Thµnh phè Hå ChÝ Minh, ViÖt Nam</t>
-  </si>
-  <si>
-    <t>c«ng ty tnhh mét thµnh viªn x©y l¾p ®iÖn thµnh nam</t>
-  </si>
-  <si>
-    <t>84/17C NguyÔn BiÓu, Ph­êng 01, QuËn 5, Thµnh phè Hå ChÝ Minh, ViÖt Nam</t>
-  </si>
-  <si>
-    <t>0315262270</t>
-  </si>
-  <si>
-    <t>0312671758</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -378,9 +303,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -418,7 +343,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -490,7 +415,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -663,23 +588,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" style="19" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="21" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" style="23" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="26" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" style="27" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="26" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.81640625" style="19" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" customWidth="1"/>
+    <col min="4" max="4" width="20.453125" style="23" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" style="26" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" style="27" customWidth="1"/>
+    <col min="7" max="7" width="11.54296875" style="26" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B1" s="20" t="s">
         <v>0</v>
@@ -688,7 +613,7 @@
         <v>6</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E1" s="24" t="s">
         <v>1</v>
@@ -700,98 +625,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="19">
-        <v>753</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="26">
-        <v>60</v>
-      </c>
-      <c r="F2" s="27">
-        <v>16666.66</v>
-      </c>
-      <c r="G2" s="26">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="19">
-        <v>754</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="26">
-        <v>15</v>
-      </c>
-      <c r="F3" s="27">
-        <v>23148.15</v>
-      </c>
-      <c r="G3" s="26">
-        <v>347222</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="19">
-        <v>755</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="26">
-        <v>15</v>
-      </c>
-      <c r="F4" s="27">
-        <v>18518.509999999998</v>
-      </c>
-      <c r="G4" s="26">
-        <v>277778</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="19">
-        <v>756</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="26">
-        <v>10</v>
-      </c>
-      <c r="F5" s="27">
-        <v>60185.18</v>
-      </c>
-      <c r="G5" s="26">
-        <v>601852</v>
-      </c>
-    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -799,66 +634,66 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="8" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.54296875" style="8" customWidth="1"/>
     <col min="5" max="5" width="29" style="8" customWidth="1"/>
-    <col min="6" max="6" width="23.28515625" style="8" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="8" customWidth="1"/>
-    <col min="8" max="9" width="17.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" style="1"/>
-    <col min="15" max="15" width="8.85546875" style="8"/>
-    <col min="16" max="16384" width="8.85546875" style="1"/>
+    <col min="6" max="6" width="23.26953125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" style="8" customWidth="1"/>
+    <col min="8" max="9" width="17.453125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.26953125" style="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.26953125" style="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.81640625" style="1"/>
+    <col min="15" max="15" width="8.81640625" style="8"/>
+    <col min="16" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="3" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="J1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="K1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="L1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="M1" s="16" t="s">
         <v>17</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" s="16" t="s">
-        <v>19</v>
       </c>
       <c r="N1" s="6" t="s">
         <v>7</v>
@@ -867,195 +702,39 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="10">
-        <v>753</v>
-      </c>
-      <c r="C2" s="12">
-        <v>45598</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="17">
-        <v>1000000</v>
-      </c>
-      <c r="K2" s="8">
-        <v>8</v>
-      </c>
-      <c r="L2" s="17">
-        <v>80000</v>
-      </c>
-      <c r="M2" s="17">
-        <v>1080000</v>
-      </c>
-      <c r="N2" s="1">
-        <v>1</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="10">
-        <v>754</v>
-      </c>
-      <c r="C3" s="12">
-        <v>45598</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="17">
-        <v>347222</v>
-      </c>
-      <c r="K3" s="8">
-        <v>8</v>
-      </c>
-      <c r="L3" s="17">
-        <v>27778</v>
-      </c>
-      <c r="M3" s="17">
-        <v>375000</v>
-      </c>
-      <c r="N3" s="1">
-        <v>1</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="10">
-        <v>755</v>
-      </c>
-      <c r="C4" s="12">
-        <v>45599</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="17">
-        <v>277778</v>
-      </c>
-      <c r="K4" s="8">
-        <v>8</v>
-      </c>
-      <c r="L4" s="17">
-        <v>22222</v>
-      </c>
-      <c r="M4" s="17">
-        <v>300000</v>
-      </c>
-      <c r="N4" s="1">
-        <v>1</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="10">
-        <v>756</v>
-      </c>
-      <c r="C5" s="12">
-        <v>45602</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="17">
-        <v>865741</v>
-      </c>
-      <c r="K5" s="8">
-        <v>8</v>
-      </c>
-      <c r="L5" s="17">
-        <v>69259</v>
-      </c>
-      <c r="M5" s="17">
-        <v>935000</v>
-      </c>
-      <c r="N5" s="1">
-        <v>1</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B2" s="10"/>
+      <c r="C2" s="12"/>
+      <c r="E2" s="13"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B3" s="10"/>
+      <c r="C3" s="12"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="10"/>
+      <c r="C4" s="12"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B5" s="10"/>
+      <c r="C5" s="12"/>
+      <c r="E5" s="13"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B6" s="10"/>
       <c r="C6" s="12"/>
       <c r="E6" s="13"/>
@@ -1063,10 +742,10 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C7" s="12"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C8" s="12"/>
     </row>
   </sheetData>
